--- a/diseases/d132/2020-2025.xlsx
+++ b/diseases/d132/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1650,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2387,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3124,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.001928324877773368</v>
       </c>
@@ -4021,9 +4009,6 @@
       <c r="O24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.003856649755546737</v>
       </c>
@@ -4761,9 +4746,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.001928324877773368</v>
       </c>
@@ -5501,9 +5483,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6389,9 +6368,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.001928324877773368</v>
       </c>
@@ -7129,9 +7105,6 @@
       <c r="O45" t="n">
         <v>3</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.005784974633320106</v>
       </c>
@@ -7869,9 +7842,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.001928324877773368</v>
       </c>
@@ -8757,9 +8727,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9497,9 +9464,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10349,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11125,9 +11086,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11865,9 +11823,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12605,9 +12560,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.001928699917871136</v>
       </c>
@@ -13493,9 +13445,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14233,9 +14182,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14973,9 +14919,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15861,9 +15804,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.001928699917871136</v>
       </c>
@@ -16601,9 +16541,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17489,9 +17426,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18229,9 +18163,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -18969,9 +18900,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.001928699917871136</v>
       </c>
@@ -19857,9 +19785,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -21189,9 +21114,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -22521,9 +22443,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.001931153918635252</v>
       </c>
@@ -24001,9 +23920,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -25481,9 +25397,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -26813,9 +26726,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -28293,9 +28203,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -29773,9 +29680,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -31105,9 +31009,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -32585,9 +32486,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -34065,9 +33963,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -35397,9 +35292,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -37025,9 +36917,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -38357,9 +38246,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -39689,9 +39575,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -41169,9 +41052,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -42649,9 +42529,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -43981,9 +43858,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -45461,9 +45335,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -46941,9 +46812,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -48421,9 +48289,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -49901,9 +49766,6 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0</v>
       </c>
@@ -51233,9 +51095,6 @@
       <c r="O343" t="n">
         <v>2</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0.003864828474371134</v>
       </c>
@@ -52713,9 +52572,6 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0</v>
       </c>
@@ -54193,9 +54049,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -55525,9 +55378,6 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
@@ -57005,9 +56855,6 @@
       <c r="O382" t="n">
         <v>0</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0</v>
       </c>
@@ -58485,9 +58332,6 @@
       <c r="O392" t="n">
         <v>0</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0</v>
       </c>
@@ -59817,9 +59661,6 @@
       <c r="O401" t="n">
         <v>0</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0</v>
       </c>
@@ -61297,9 +61138,6 @@
       <c r="O411" t="n">
         <v>1</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
       <c r="R411" t="n">
         <v>0.00193357811143172</v>
       </c>
@@ -62777,9 +62615,6 @@
       <c r="O421" t="n">
         <v>0</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0</v>
       </c>
@@ -64109,9 +63944,6 @@
       <c r="O430" t="n">
         <v>0</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>0</v>
       </c>
@@ -65737,9 +65569,6 @@
       <c r="O441" t="n">
         <v>0</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0</v>
       </c>
@@ -67069,9 +66898,6 @@
       <c r="O450" t="n">
         <v>0</v>
       </c>
-      <c r="Q450" t="n">
-        <v>0</v>
-      </c>
       <c r="R450" t="n">
         <v>0</v>
       </c>
@@ -68549,9 +68375,6 @@
       <c r="O460" t="n">
         <v>0</v>
       </c>
-      <c r="Q460" t="n">
-        <v>0</v>
-      </c>
       <c r="R460" t="n">
         <v>0</v>
       </c>
@@ -70029,9 +69852,6 @@
       <c r="O470" t="n">
         <v>0</v>
       </c>
-      <c r="Q470" t="n">
-        <v>0</v>
-      </c>
       <c r="R470" t="n">
         <v>0</v>
       </c>
@@ -71361,9 +71181,6 @@
       <c r="O479" t="n">
         <v>0</v>
       </c>
-      <c r="Q479" t="n">
-        <v>0</v>
-      </c>
       <c r="R479" t="n">
         <v>0</v>
       </c>
@@ -72841,9 +72658,6 @@
       <c r="O489" t="n">
         <v>1</v>
       </c>
-      <c r="Q489" t="n">
-        <v>0</v>
-      </c>
       <c r="R489" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -74173,9 +73987,6 @@
       <c r="O498" t="n">
         <v>0</v>
       </c>
-      <c r="Q498" t="n">
-        <v>0</v>
-      </c>
       <c r="R498" t="n">
         <v>0</v>
       </c>
@@ -75653,9 +75464,6 @@
       <c r="O508" t="n">
         <v>0</v>
       </c>
-      <c r="Q508" t="n">
-        <v>0</v>
-      </c>
       <c r="R508" t="n">
         <v>0</v>
       </c>
@@ -76985,9 +76793,6 @@
       <c r="O517" t="n">
         <v>0</v>
       </c>
-      <c r="Q517" t="n">
-        <v>0</v>
-      </c>
       <c r="R517" t="n">
         <v>0</v>
       </c>
@@ -78613,9 +78418,6 @@
       <c r="O528" t="n">
         <v>0</v>
       </c>
-      <c r="Q528" t="n">
-        <v>0</v>
-      </c>
       <c r="R528" t="n">
         <v>0</v>
       </c>
@@ -79945,9 +79747,6 @@
       <c r="O537" t="n">
         <v>1</v>
       </c>
-      <c r="Q537" t="n">
-        <v>0</v>
-      </c>
       <c r="R537" t="n">
         <v>0.001935470278971621</v>
       </c>
@@ -81425,9 +81224,6 @@
       <c r="O547" t="n">
         <v>0</v>
       </c>
-      <c r="Q547" t="n">
-        <v>0</v>
-      </c>
       <c r="R547" t="n">
         <v>0</v>
       </c>
@@ -82905,9 +82701,6 @@
       <c r="O557" t="n">
         <v>0</v>
       </c>
-      <c r="Q557" t="n">
-        <v>0</v>
-      </c>
       <c r="R557" t="n">
         <v>0</v>
       </c>
@@ -84237,9 +84030,6 @@
       <c r="O566" t="n">
         <v>0</v>
       </c>
-      <c r="Q566" t="n">
-        <v>0</v>
-      </c>
       <c r="R566" t="n">
         <v>0</v>
       </c>
@@ -85717,9 +85507,6 @@
       <c r="O576" t="n">
         <v>0</v>
       </c>
-      <c r="Q576" t="n">
-        <v>0</v>
-      </c>
       <c r="R576" t="n">
         <v>0</v>
       </c>
@@ -87195,9 +86982,6 @@
         <v>0</v>
       </c>
       <c r="O586" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q586" t="n">
         <v>0</v>
       </c>
       <c r="R586" t="n">
